--- a/data/trans_bre/P15A-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P15A-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,2; -1,9</t>
+          <t>-7,3; -2,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,09; -0,32</t>
+          <t>-4,94; -0,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; -0,87</t>
+          <t>-5,13; -0,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,81</t>
+          <t>-2,35; 5,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-83,43; -33,18</t>
+          <t>-84,06; -33,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-81,47; -2,81</t>
+          <t>-80,55; -4,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-89,78; -14,08</t>
+          <t>-89,84; -9,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,49; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 0,49</t>
+          <t>-4,17; 0,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,9; -0,83</t>
+          <t>-4,89; -0,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,88; -0,07</t>
+          <t>-4,1; -0,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,44; -0,04</t>
+          <t>-4,46; 0,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,11; 14,36</t>
+          <t>-68,49; 6,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,94; -16,01</t>
+          <t>-81,76; -14,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-80,38; 8,19</t>
+          <t>-81,71; -10,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-93,69; 13,48</t>
+          <t>-93,11; 24,86</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,24</t>
+          <t>-2,17; 1,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,9</t>
+          <t>-2,56; 0,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,4</t>
+          <t>-3,0; 0,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,14</t>
+          <t>-1,85; 1,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,0; 94,23</t>
+          <t>-65,93; 80,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-69,89; 83,09</t>
+          <t>-74,52; 59,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-77,74; 24,5</t>
+          <t>-74,95; 38,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-65,5; 110,98</t>
+          <t>-63,21; 116,46</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 0,1</t>
+          <t>-3,95; 0,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,88</t>
+          <t>0,36; 3,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,04</t>
+          <t>-2,04; 1,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,42</t>
+          <t>-2,49; 1,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,29; 12,02</t>
+          <t>-78,7; 19,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 496,65</t>
+          <t>6,09; 496,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,82; 109,31</t>
+          <t>-70,88; 107,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,42; 124,14</t>
+          <t>-67,66; 69,89</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 2,05</t>
+          <t>-2,34; 1,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 4,1</t>
+          <t>0,35; 4,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,01</t>
+          <t>0,38; 4,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,48</t>
+          <t>-0,08; 2,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-63,42; 154,89</t>
+          <t>-65,37; 138,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 1025,48</t>
+          <t>-7,8; 1136,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 1283,75</t>
+          <t>-0,35; 1593,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 360,04</t>
+          <t>-10,63; 384,17</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,52</t>
+          <t>-1,09; 3,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,8</t>
+          <t>-1,71; 3,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,77</t>
+          <t>0,59; 5,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,15</t>
+          <t>-1,51; 3,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,28; 592,02</t>
+          <t>-52,76; 488,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 328,9</t>
+          <t>-44,13; 257,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,7; 1032,19</t>
+          <t>1,17; 876,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-43,63; 254,04</t>
+          <t>-49,78; 242,58</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 7,6</t>
+          <t>0,36; 7,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 4,7</t>
+          <t>-1,91; 4,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 5,46</t>
+          <t>-0,89; 5,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,57</t>
+          <t>1,06; 5,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 590,22</t>
+          <t>-7,71; 510,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-39,87; 260,97</t>
+          <t>-38,29; 247,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 287,91</t>
+          <t>-25,84; 306,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,55; 275,53</t>
+          <t>26,37; 309,27</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,88; -0,16</t>
+          <t>-1,89; 0,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,74</t>
+          <t>-0,9; 0,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,68</t>
+          <t>-0,97; 0,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,24</t>
+          <t>-0,42; 1,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,11; -4,51</t>
+          <t>-44,44; -0,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 30,62</t>
+          <t>-27,6; 27,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 29,27</t>
+          <t>-33,54; 25,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 72,31</t>
+          <t>-15,6; 69,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P15A-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P15A-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,3; -2,11</t>
+          <t>-7,54; -2,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,94; -0,33</t>
+          <t>-4,89; -0,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,13; -0,77</t>
+          <t>-5,29; -0,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 5,12</t>
+          <t>-3,19; 4,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-84,06; -33,39</t>
+          <t>-86,07; -38,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,55; -4,1</t>
+          <t>-82,23; -5,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-89,84; -9,19</t>
+          <t>-91,09; -16,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-89,49; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,79</t>
+          <t>-2,29</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-64,44%</t>
+          <t>-69,37%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,22</t>
+          <t>-4,12; 0,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -0,66</t>
+          <t>-5,03; -0,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,1; -0,36</t>
+          <t>-3,99; -0,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 0,09</t>
+          <t>-5,18; -0,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,49; 6,29</t>
+          <t>-68,51; 7,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,76; -14,78</t>
+          <t>-81,31; -17,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-81,71; -10,54</t>
+          <t>-82,24; -5,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-93,11; 24,86</t>
+          <t>-93,45; -6,79</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-9,42%</t>
+          <t>-13,15%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,09</t>
+          <t>-2,03; 1,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,75</t>
+          <t>-2,17; 0,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,59</t>
+          <t>-3,18; 0,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,12</t>
+          <t>-1,79; 1,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,93; 80,68</t>
+          <t>-63,93; 84,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-74,52; 59,91</t>
+          <t>-69,81; 63,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-74,95; 38,8</t>
+          <t>-75,52; 15,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-63,21; 116,46</t>
+          <t>-60,63; 109,19</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-1,47</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-32,78%</t>
+          <t>-45,84%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 0,33</t>
+          <t>-3,97; 0,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,84</t>
+          <t>0,23; 3,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,09</t>
+          <t>-1,91; 1,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,0</t>
+          <t>-3,33; 0,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-78,7; 19,46</t>
+          <t>-78,07; 8,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 496,48</t>
+          <t>3,73; 458,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,88; 107,9</t>
+          <t>-72,06; 95,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,66; 69,89</t>
+          <t>-71,93; 11,45</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100,36%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,94</t>
+          <t>-2,41; 2,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,19</t>
+          <t>0,37; 4,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,11</t>
+          <t>0,43; 4,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,5</t>
+          <t>-0,11; 2,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-65,37; 138,5</t>
+          <t>-64,82; 163,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 1136,64</t>
+          <t>-8,61; 1002,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1593,54</t>
+          <t>2,5; 1260,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 384,17</t>
+          <t>-10,6; 356,93</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>2,55</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>148,35%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,2</t>
+          <t>-1,26; 3,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,51</t>
+          <t>-1,78; 3,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,29</t>
+          <t>0,74; 5,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,02</t>
+          <t>1,1; 4,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,76; 488,48</t>
+          <t>-55,04; 446,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,13; 257,03</t>
+          <t>-47,81; 257,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 876,98</t>
+          <t>14,71; 848,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,78; 242,58</t>
+          <t>32,77; 408,94</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>108,33%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 7,27</t>
+          <t>0,07; 7,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 4,78</t>
+          <t>-1,71; 4,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 5,49</t>
+          <t>-0,75; 5,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,64</t>
+          <t>0,84; 5,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 510,53</t>
+          <t>-8,53; 668,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-38,29; 247,42</t>
+          <t>-39,09; 255,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-25,84; 306,07</t>
+          <t>-21,78; 272,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26,37; 309,27</t>
+          <t>16,31; 277,56</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,01</t>
+          <t>-1,83; -0,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,7</t>
+          <t>-0,96; 0,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,58</t>
+          <t>-0,9; 0,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,18</t>
+          <t>-0,41; 1,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,44; -0,01</t>
+          <t>-43,63; -4,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,6; 27,58</t>
+          <t>-28,15; 26,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-33,54; 25,8</t>
+          <t>-30,35; 30,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 69,62</t>
+          <t>-14,28; 62,47</t>
         </is>
       </c>
     </row>
